--- a/data/_shared/logs/_training_log.xlsx
+++ b/data/_shared/logs/_training_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1052,6 +1052,74 @@
         <v>-66.65459598117215</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-11T19:04:25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>593712ff0</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>./data/england/modeling/2026-09-11/models</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="n">
+        <v>45.04011175173255</v>
+      </c>
+      <c r="L10" t="n">
+        <v>45.04011175173255</v>
+      </c>
+      <c r="M10" t="n">
+        <v>50.50505050505051</v>
+      </c>
+      <c r="N10" t="n">
+        <v>50.50505050505051</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-19.21379530603816</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-19.21379530603816</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-77.54048531187325</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-77.54048531187325</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/_shared/logs/_training_log.xlsx
+++ b/data/_shared/logs/_training_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1120,6 +1120,346 @@
         <v>-77.54048531187325</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-11T19:15:23</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>16617e5fe</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>./data/england/modeling/2026-09-11/models</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="n">
+        <v>41.37254901960785</v>
+      </c>
+      <c r="L11" t="n">
+        <v>41.37254901960785</v>
+      </c>
+      <c r="M11" t="n">
+        <v>46.46464646464646</v>
+      </c>
+      <c r="N11" t="n">
+        <v>46.46464646464646</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-47.14836589374595</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-47.14836589374595</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-53.67111036603984</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-53.67111036603984</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-12T01:38:17</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>16617e5fe</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>382.9</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>./data/france/modeling/2026-09-11/models</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="n">
+        <v>37.14497687003578</v>
+      </c>
+      <c r="L12" t="n">
+        <v>37.14497687003578</v>
+      </c>
+      <c r="M12" t="n">
+        <v>45.16129032258064</v>
+      </c>
+      <c r="N12" t="n">
+        <v>45.16129032258064</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-60.50308245296514</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-60.50308245296514</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-34.97755389353787</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-34.97755389353787</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-12T22:58:54</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ac26402b6</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>197.2</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>./data/germany/modeling/2026-09-12/models</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>43.75503626107977</v>
+      </c>
+      <c r="L13" t="n">
+        <v>43.75503626107977</v>
+      </c>
+      <c r="M13" t="n">
+        <v>50</v>
+      </c>
+      <c r="N13" t="n">
+        <v>50</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-8.650800081887255</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-8.650800081887255</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>15.82003802326102</v>
+      </c>
+      <c r="R13" t="n">
+        <v>15.82003802326102</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-13T07:22:24</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ac26402b6</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>503.4</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>./data/italy/modeling/2026-09-12/models</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>48.03436743489637</v>
+      </c>
+      <c r="L14" t="n">
+        <v>48.03436743489637</v>
+      </c>
+      <c r="M14" t="n">
+        <v>54</v>
+      </c>
+      <c r="N14" t="n">
+        <v>54</v>
+      </c>
+      <c r="O14" t="n">
+        <v>7.559487539008643</v>
+      </c>
+      <c r="P14" t="n">
+        <v>7.559487539008643</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-9.541295311183561</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-9.541295311183561</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-13T14:29:36</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ac26402b6</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>427.2</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>./data/spain/modeling/2026-09-13/models</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="n">
+        <v>43.82645803698435</v>
+      </c>
+      <c r="L15" t="n">
+        <v>43.82645803698435</v>
+      </c>
+      <c r="M15" t="n">
+        <v>51</v>
+      </c>
+      <c r="N15" t="n">
+        <v>51</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-15.30496264986677</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-15.30496264986677</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-35.03462237398661</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-35.03462237398661</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/_shared/logs/_training_log.xlsx
+++ b/data/_shared/logs/_training_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1460,6 +1460,346 @@
         <v>-35.03462237398661</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-13T18:02:53</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>6e136e5a8</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>./data/england/modeling/2026-09-11/models</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="n">
+        <v>40.77104526020934</v>
+      </c>
+      <c r="L16" t="n">
+        <v>40.77104526020934</v>
+      </c>
+      <c r="M16" t="n">
+        <v>47.47474747474747</v>
+      </c>
+      <c r="N16" t="n">
+        <v>47.47474747474747</v>
+      </c>
+      <c r="O16" t="n">
+        <v>-44.88129952586834</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-44.88129952586834</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-71.45066712405047</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-71.45066712405047</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-13T18:07:54</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>6e136e5a8</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>5</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>./data/england/modeling/2026-09-11/models</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="n">
+        <v>41.54040404040404</v>
+      </c>
+      <c r="L17" t="n">
+        <v>41.54040404040404</v>
+      </c>
+      <c r="M17" t="n">
+        <v>48.48484848484848</v>
+      </c>
+      <c r="N17" t="n">
+        <v>48.48484848484848</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-40.31273627937431</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-40.31273627937431</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-69.00749400630026</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-69.00749400630026</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-13T18:14:58</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>6e136e5a8</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>./data/england/modeling/2026-09-11/models</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="n">
+        <v>40.77104526020934</v>
+      </c>
+      <c r="L18" t="n">
+        <v>40.77104526020934</v>
+      </c>
+      <c r="M18" t="n">
+        <v>47.47474747474747</v>
+      </c>
+      <c r="N18" t="n">
+        <v>47.47474747474747</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-44.8893091611186</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-44.8893091611186</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-71.42451180395624</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-71.42451180395624</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-13T18:20:01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>6e136e5a8</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>./data/england/modeling/2026-09-11/models</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="n">
+        <v>40.77104526020934</v>
+      </c>
+      <c r="L19" t="n">
+        <v>40.77104526020934</v>
+      </c>
+      <c r="M19" t="n">
+        <v>47.47474747474747</v>
+      </c>
+      <c r="N19" t="n">
+        <v>47.47474747474747</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-44.8893091611186</v>
+      </c>
+      <c r="P19" t="n">
+        <v>-44.8893091611186</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-71.42451180395624</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-71.42451180395624</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-13T18:33:13</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>6e136e5a8</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>smoke</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>./data/england/modeling/2026-09-11/models</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="n">
+        <v>45.30270485658286</v>
+      </c>
+      <c r="L20" t="n">
+        <v>45.30270485658286</v>
+      </c>
+      <c r="M20" t="n">
+        <v>53.06407035175879</v>
+      </c>
+      <c r="N20" t="n">
+        <v>53.06407035175879</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-25.58044091601801</v>
+      </c>
+      <c r="P20" t="n">
+        <v>-25.58044091601801</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-39.03397434581655</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-39.03397434581655</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
